--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,11 @@
       <c r="AB4" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1223,7 +1227,11 @@
       <c r="AB5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1942,7 +1950,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -2459,7 +2471,11 @@
       <c r="AB17" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2661,7 +2677,11 @@
       <c r="AB19" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2762,7 +2782,11 @@
       <c r="AB20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -4091,7 +4115,11 @@
       <c r="AB33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -5125,7 +5153,11 @@
       <c r="AB43" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5327,7 +5359,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5832,7 +5868,11 @@
       <c r="AB50" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -7177,7 +7217,11 @@
       <c r="AB63" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 9 clubs short</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="P20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" s="10" t="n">
         <v>1</v>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5657,8 +5657,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6365,8 +6365,8 @@
       <c r="T55" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U55" s="9" t="n">
-        <v>0</v>
+      <c r="U55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V55" s="9" t="n">
         <v>2</v>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6796,8 +6796,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -7713,7 +7713,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -7746,7 +7746,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -7779,7 +7779,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="R5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="9" t="n">
-        <v>1</v>
+      <c r="S5" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T5" s="10" t="n">
         <v>1</v>
@@ -2186,7 +2186,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2256,8 +2256,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4185,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>0</v>
@@ -4196,8 +4196,8 @@
       <c r="T34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
+      <c r="U34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V34" s="9" t="n">
         <v>1</v>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4413,8 +4413,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="P43" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q43" s="10" t="n">
         <v>2</v>
@@ -5803,13 +5803,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>1</v>
@@ -5851,7 +5851,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>7</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6279,8 +6279,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -7482,7 +7482,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -7614,7 +7614,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -7746,7 +7746,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -956,17 +956,17 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M3" s="8" t="n">
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1057,17 +1057,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1314,8 +1314,8 @@
       <c r="V6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W6" s="9" t="n">
-        <v>2</v>
+      <c r="W6" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>6</v>
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1578,17 +1578,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M9" s="8" t="n">
@@ -1622,8 +1622,8 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>2</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -2095,17 +2095,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2348,8 +2348,8 @@
       <c r="V16" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>3</v>
+      <c r="W16" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>5</v>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2612,13 +2612,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2717,13 +2717,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -2743,8 +2743,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P20" s="9" t="n">
-        <v>3</v>
+      <c r="P20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>0</v>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>5</v>
@@ -3024,17 +3024,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="8" t="n">
@@ -3072,7 +3072,7 @@
         <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>6</v>
@@ -3129,13 +3129,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="S25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="9" t="n">
         <v>0</v>
@@ -3335,13 +3335,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3537,13 +3537,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3584,8 +3584,8 @@
       <c r="V28" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W28" s="9" t="n">
-        <v>2</v>
+      <c r="W28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>7</v>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
@@ -3848,13 +3848,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -3949,13 +3949,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4155,13 +4155,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
@@ -4256,13 +4256,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4401,8 +4401,8 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>3</v>
+      <c r="V36" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4567,17 +4567,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="8" t="n">
@@ -4612,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4773,17 +4773,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4878,13 +4878,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>1</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -5088,13 +5088,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>7</v>
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5238,7 +5238,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5341,8 +5341,8 @@
       <c r="V45" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>3</v>
+      <c r="W45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -5500,13 +5500,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5601,17 +5601,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="10" t="n">
         <v>1</v>
@@ -5702,17 +5702,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5803,13 +5803,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>7</v>
+        <v>-9</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5908,13 +5908,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -6013,17 +6013,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6118,13 +6118,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6159,8 +6159,8 @@
       <c r="T53" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
+      <c r="U53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V53" s="9" t="n">
         <v>3</v>
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6324,17 +6324,17 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M55" s="8" t="n">
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6534,13 +6534,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6740,13 +6740,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6841,17 +6841,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L60" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="8" t="n">
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7033,7 +7033,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7047,13 +7047,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7082,8 +7082,8 @@
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="9" t="n">
-        <v>1</v>
+      <c r="S62" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T62" s="10" t="n">
         <v>1</v>
@@ -7091,11 +7091,11 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>1</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>7</v>
@@ -7152,13 +7152,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
+        <v>-11</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7257,17 +7257,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7416,7 +7416,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -7449,7 +7449,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -7482,13 +7482,13 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -7515,13 +7515,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -7563,7 +7563,7 @@
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7581,7 +7581,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -7614,7 +7614,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -7662,7 +7662,7 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -7680,7 +7680,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -7728,7 +7728,7 @@
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -7746,13 +7746,13 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -7761,7 +7761,7 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7794,7 +7794,7 @@
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7812,7 +7812,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
@@ -1267,13 +1267,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="9" t="n">
         <v>0</v>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3785,8 +3785,8 @@
       <c r="S30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="9" t="n">
-        <v>0</v>
+      <c r="T30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U30" s="9" t="n">
         <v>0</v>
@@ -3848,13 +3848,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -4773,13 +4773,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5012,8 +5012,8 @@
       <c r="P42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>1</v>
+      <c r="Q42" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
@@ -5088,13 +5088,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>7</v>
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>4</v>
       </c>
       <c r="W45" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X45" s="10" t="n">
         <v>7</v>
@@ -6160,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V53" s="9" t="n">
         <v>3</v>
@@ -6429,13 +6429,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7152,13 +7152,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7196,8 +7196,8 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>3</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -7647,7 +7647,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -7812,7 +7812,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>

--- a/docs/d/17/inyear.xlsx
+++ b/docs/d/17/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,14 +574,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 6 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 6 clubs short</t>
         </is>
       </c>
     </row>
@@ -1683,13 +1683,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -3024,13 +3024,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3129,13 +3129,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -3642,13 +3642,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3848,13 +3848,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3892,8 +3892,8 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>3</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W31" s="9" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4500,8 +4500,8 @@
       <c r="S37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T37" s="9" t="n">
-        <v>0</v>
+      <c r="T37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U37" s="9" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>0</v>
@@ -5220,7 +5220,7 @@
         </is>
       </c>
       <c r="P44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -5601,13 +5601,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>1</v>
@@ -5702,13 +5702,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5829,8 +5829,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P50" s="9" t="n">
-        <v>3</v>
+      <c r="P50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q50" s="9" t="n">
         <v>1</v>
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -6946,13 +6946,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -7614,7 +7614,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -7713,7 +7713,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
